--- a/My_Personal_Reviews/Copy_UTS-5_Skor.xlsx
+++ b/My_Personal_Reviews/Copy_UTS-5_Skor.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felissha/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/felissha/Documents/GitHub/all/new-all-about-me/My_Personal_Reviews/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F59AD4-06C6-5A48-9585-7B1B0973AE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D299B2F-3318-F74E-B991-C0E7B98AC8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="740" windowWidth="27640" windowHeight="16920" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
+    <workbookView xWindow="1580" yWindow="740" windowWidth="27640" windowHeight="16920" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,8 +24,11 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -101,66 +104,6 @@
     <t>UTS-4_Rata2</t>
   </si>
   <si>
-    <t>UAS-1_Kejelasan</t>
-  </si>
-  <si>
-    <t>UAS-1_Logika</t>
-  </si>
-  <si>
-    <t>UAS-1_Validitas (Bukti/Contoh)</t>
-  </si>
-  <si>
-    <t>UAS-1_Kegunaan</t>
-  </si>
-  <si>
-    <t>UAS-1_Rata2</t>
-  </si>
-  <si>
-    <t>UAS-2_Menarik (Compelling)</t>
-  </si>
-  <si>
-    <t>UAS-2_Informatif</t>
-  </si>
-  <si>
-    <t>UAS-2_Persuasif</t>
-  </si>
-  <si>
-    <t>UAS-2_Menggugah (Engaging)</t>
-  </si>
-  <si>
-    <t>UAS-2_Rata2</t>
-  </si>
-  <si>
-    <t>UAS-3_Konten</t>
-  </si>
-  <si>
-    <t>UAS-3_Organisasi</t>
-  </si>
-  <si>
-    <t>UAS-3_Penyajian (Delivery)</t>
-  </si>
-  <si>
-    <t>UAS-3_Keterlibatan Audiens</t>
-  </si>
-  <si>
-    <t>UAS-3_Rata2</t>
-  </si>
-  <si>
-    <t>UAS-4_Orisinalitas</t>
-  </si>
-  <si>
-    <t>UAS-4_Kejelasan</t>
-  </si>
-  <si>
-    <t>UAS-4_Kelayakan (Feasibility)</t>
-  </si>
-  <si>
-    <t>UAS-4_Dampak</t>
-  </si>
-  <si>
-    <t>UAS-4_Rata2</t>
-  </si>
-  <si>
     <t>Isi NIM/ID</t>
   </si>
   <si>
@@ -174,6 +117,15 @@
   </si>
   <si>
     <t>Felissha Dunell</t>
+  </si>
+  <si>
+    <t>Hanan Fitra Salam</t>
+  </si>
+  <si>
+    <t>Muhammad Faris Daffa</t>
+  </si>
+  <si>
+    <t>Sherry Eunike</t>
   </si>
 </sst>
 </file>
@@ -636,334 +588,444 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="AA2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AP2" s="3"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>18223099</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="4" t="str">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
-      </c>
-      <c r="L3" s="4" t="str">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2">
+        <v>5</v>
+      </c>
+      <c r="L3" s="4">
         <f t="shared" ref="L3:L66" si="1">IF(COUNT(H3:K3)=0,"",AVERAGE(H3:K3))</f>
-        <v/>
-      </c>
-      <c r="Q3" s="4" t="str">
+        <v>5</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5</v>
+      </c>
+      <c r="N3" s="2">
+        <v>5</v>
+      </c>
+      <c r="O3" s="2">
+        <v>5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="4">
         <f t="shared" ref="Q3:Q66" si="2">IF(COUNT(M3:P3)=0,"",AVERAGE(M3:P3))</f>
-        <v/>
-      </c>
-      <c r="V3" s="4" t="str">
-        <f t="shared" ref="V3:V66" si="3">IF(COUNT(R3:U3)=0,"",AVERAGE(R3:U3))</f>
-        <v/>
-      </c>
-      <c r="AA3" s="4" t="str">
-        <f t="shared" ref="AA3:AA66" si="4">IF(COUNT(W3:Z3)=0,"",AVERAGE(W3:Z3))</f>
-        <v/>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R3" s="2">
+        <v>5</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5</v>
+      </c>
+      <c r="T3" s="2">
+        <v>5</v>
+      </c>
+      <c r="U3" s="2">
+        <v>5</v>
+      </c>
+      <c r="V3" s="4">
+        <v>5</v>
+      </c>
+      <c r="AA3" s="4"/>
       <c r="AF3" s="4" t="str">
-        <f t="shared" ref="AF3:AF66" si="5">IF(COUNT(AB3:AE3)=0,"",AVERAGE(AB3:AE3))</f>
+        <f t="shared" ref="AF3:AF66" si="3">IF(COUNT(AB3:AE3)=0,"",AVERAGE(AB3:AE3))</f>
         <v/>
       </c>
       <c r="AK3" s="4" t="str">
-        <f t="shared" ref="AK3:AK66" si="6">IF(COUNT(AG3:AJ3)=0,"",AVERAGE(AG3:AJ3))</f>
+        <f t="shared" ref="AK3:AK66" si="4">IF(COUNT(AG3:AJ3)=0,"",AVERAGE(AG3:AJ3))</f>
         <v/>
       </c>
       <c r="AP3" s="4" t="str">
-        <f t="shared" ref="AP3:AP66" si="7">IF(COUNT(AL3:AO3)=0,"",AVERAGE(AL3:AO3))</f>
+        <f t="shared" ref="AP3:AP66" si="5">IF(COUNT(AL3:AO3)=0,"",AVERAGE(AL3:AO3))</f>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L4" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q4" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V4" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A4" s="2">
+        <v>18222133</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>3.75</v>
+      </c>
+      <c r="H4" s="2">
+        <v>4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>4</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" si="1"/>
+        <v>3.75</v>
+      </c>
+      <c r="M4" s="2">
+        <v>4</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4</v>
+      </c>
+      <c r="O4" s="2">
+        <v>4</v>
+      </c>
+      <c r="P4" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="R4" s="2">
+        <v>3</v>
+      </c>
+      <c r="S4" s="2">
+        <v>4</v>
+      </c>
+      <c r="T4" s="2">
+        <v>3</v>
+      </c>
+      <c r="U4" s="2">
+        <v>4</v>
+      </c>
+      <c r="V4" s="4">
+        <f t="shared" ref="V3:V66" si="6">IF(COUNT(R4:U4)=0,"",AVERAGE(R4:U4))</f>
+        <v>3.5</v>
       </c>
       <c r="AA4" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AA3:AA66" si="7">IF(COUNT(W4:Z4)=0,"",AVERAGE(W4:Z4))</f>
         <v/>
       </c>
       <c r="AF4" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK4" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP4" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L5" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q5" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V5" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="2">
+        <v>18224075</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" si="1"/>
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>5</v>
+      </c>
+      <c r="O5" s="2">
+        <v>5</v>
+      </c>
+      <c r="P5" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="R5" s="2">
+        <v>5</v>
+      </c>
+      <c r="S5" s="2">
+        <v>5</v>
+      </c>
+      <c r="T5" s="2">
+        <v>5</v>
+      </c>
+      <c r="U5" s="2">
+        <v>5</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="AA5" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF5" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK5" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP5" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L6" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="Q6" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V6" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>18224025</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>4</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" si="1"/>
+        <v>3.75</v>
+      </c>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
+      <c r="N6" s="2">
+        <v>5</v>
+      </c>
+      <c r="O6" s="2">
+        <v>5</v>
+      </c>
+      <c r="P6" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="4">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="R6" s="2">
+        <v>5</v>
+      </c>
+      <c r="S6" s="2">
+        <v>5</v>
+      </c>
+      <c r="T6" s="2">
+        <v>5</v>
+      </c>
+      <c r="U6" s="2">
+        <v>5</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="AA6" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF6" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK6" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP6" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -981,23 +1043,23 @@
         <v/>
       </c>
       <c r="V7" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA7" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF7" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK7" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP7" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1015,23 +1077,23 @@
         <v/>
       </c>
       <c r="V8" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA8" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF8" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK8" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP8" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1049,23 +1111,23 @@
         <v/>
       </c>
       <c r="V9" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA9" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF9" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK9" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP9" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1083,23 +1145,23 @@
         <v/>
       </c>
       <c r="V10" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA10" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF10" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK10" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP10" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1117,23 +1179,23 @@
         <v/>
       </c>
       <c r="V11" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA11" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF11" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK11" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP11" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1151,23 +1213,23 @@
         <v/>
       </c>
       <c r="V12" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA12" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF12" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK12" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP12" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1185,23 +1247,23 @@
         <v/>
       </c>
       <c r="V13" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA13" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF13" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK13" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP13" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1219,23 +1281,23 @@
         <v/>
       </c>
       <c r="V14" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA14" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF14" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK14" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP14" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1253,23 +1315,23 @@
         <v/>
       </c>
       <c r="V15" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA15" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF15" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK15" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP15" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1287,23 +1349,23 @@
         <v/>
       </c>
       <c r="V16" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA16" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF16" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK16" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP16" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1321,23 +1383,23 @@
         <v/>
       </c>
       <c r="V17" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA17" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF17" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK17" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP17" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1355,23 +1417,23 @@
         <v/>
       </c>
       <c r="V18" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA18" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF18" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK18" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP18" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1389,23 +1451,23 @@
         <v/>
       </c>
       <c r="V19" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA19" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF19" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK19" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP19" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1423,23 +1485,23 @@
         <v/>
       </c>
       <c r="V20" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA20" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF20" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK20" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP20" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1457,23 +1519,23 @@
         <v/>
       </c>
       <c r="V21" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA21" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF21" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK21" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP21" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1491,23 +1553,23 @@
         <v/>
       </c>
       <c r="V22" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA22" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF22" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK22" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP22" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1525,23 +1587,23 @@
         <v/>
       </c>
       <c r="V23" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA23" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF23" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK23" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP23" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1559,23 +1621,23 @@
         <v/>
       </c>
       <c r="V24" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA24" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF24" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK24" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP24" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1593,23 +1655,23 @@
         <v/>
       </c>
       <c r="V25" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA25" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF25" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK25" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP25" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1627,23 +1689,23 @@
         <v/>
       </c>
       <c r="V26" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA26" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF26" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK26" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP26" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1661,23 +1723,23 @@
         <v/>
       </c>
       <c r="V27" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA27" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF27" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK27" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP27" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1695,23 +1757,23 @@
         <v/>
       </c>
       <c r="V28" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA28" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF28" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK28" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP28" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1729,23 +1791,23 @@
         <v/>
       </c>
       <c r="V29" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA29" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF29" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK29" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP29" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1763,23 +1825,23 @@
         <v/>
       </c>
       <c r="V30" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA30" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF30" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK30" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP30" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1797,23 +1859,23 @@
         <v/>
       </c>
       <c r="V31" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA31" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF31" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK31" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP31" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1831,23 +1893,23 @@
         <v/>
       </c>
       <c r="V32" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA32" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF32" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK32" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP32" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1865,23 +1927,23 @@
         <v/>
       </c>
       <c r="V33" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA33" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF33" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK33" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP33" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1899,23 +1961,23 @@
         <v/>
       </c>
       <c r="V34" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA34" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF34" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK34" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP34" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1933,23 +1995,23 @@
         <v/>
       </c>
       <c r="V35" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA35" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF35" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK35" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP35" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1967,23 +2029,23 @@
         <v/>
       </c>
       <c r="V36" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA36" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF36" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK36" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP36" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2001,23 +2063,23 @@
         <v/>
       </c>
       <c r="V37" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA37" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF37" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK37" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP37" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2035,23 +2097,23 @@
         <v/>
       </c>
       <c r="V38" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA38" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF38" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK38" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP38" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2069,23 +2131,23 @@
         <v/>
       </c>
       <c r="V39" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA39" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF39" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK39" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP39" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2103,23 +2165,23 @@
         <v/>
       </c>
       <c r="V40" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA40" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF40" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK40" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP40" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2137,23 +2199,23 @@
         <v/>
       </c>
       <c r="V41" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA41" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF41" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK41" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP41" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2171,23 +2233,23 @@
         <v/>
       </c>
       <c r="V42" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA42" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF42" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK42" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP42" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2205,23 +2267,23 @@
         <v/>
       </c>
       <c r="V43" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA43" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF43" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK43" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP43" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2239,23 +2301,23 @@
         <v/>
       </c>
       <c r="V44" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA44" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF44" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK44" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP44" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2273,23 +2335,23 @@
         <v/>
       </c>
       <c r="V45" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA45" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF45" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK45" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP45" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2307,23 +2369,23 @@
         <v/>
       </c>
       <c r="V46" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA46" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF46" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK46" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP46" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2341,23 +2403,23 @@
         <v/>
       </c>
       <c r="V47" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA47" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF47" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK47" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP47" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2375,23 +2437,23 @@
         <v/>
       </c>
       <c r="V48" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA48" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF48" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK48" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP48" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2409,23 +2471,23 @@
         <v/>
       </c>
       <c r="V49" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA49" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF49" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK49" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP49" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2443,23 +2505,23 @@
         <v/>
       </c>
       <c r="V50" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA50" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF50" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK50" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP50" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2477,23 +2539,23 @@
         <v/>
       </c>
       <c r="V51" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA51" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF51" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK51" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP51" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2511,23 +2573,23 @@
         <v/>
       </c>
       <c r="V52" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA52" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF52" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK52" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP52" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2545,23 +2607,23 @@
         <v/>
       </c>
       <c r="V53" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA53" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF53" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK53" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP53" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2579,23 +2641,23 @@
         <v/>
       </c>
       <c r="V54" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA54" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF54" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK54" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP54" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2613,23 +2675,23 @@
         <v/>
       </c>
       <c r="V55" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA55" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF55" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK55" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP55" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2647,23 +2709,23 @@
         <v/>
       </c>
       <c r="V56" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA56" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF56" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK56" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP56" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2681,23 +2743,23 @@
         <v/>
       </c>
       <c r="V57" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA57" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF57" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK57" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP57" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2715,23 +2777,23 @@
         <v/>
       </c>
       <c r="V58" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA58" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF58" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK58" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP58" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2749,23 +2811,23 @@
         <v/>
       </c>
       <c r="V59" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA59" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF59" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK59" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP59" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2783,23 +2845,23 @@
         <v/>
       </c>
       <c r="V60" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA60" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF60" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK60" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP60" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2817,23 +2879,23 @@
         <v/>
       </c>
       <c r="V61" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA61" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF61" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK61" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP61" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2851,23 +2913,23 @@
         <v/>
       </c>
       <c r="V62" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA62" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF62" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK62" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP62" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2885,23 +2947,23 @@
         <v/>
       </c>
       <c r="V63" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA63" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF63" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK63" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP63" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2919,23 +2981,23 @@
         <v/>
       </c>
       <c r="V64" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA64" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF64" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK64" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP64" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2953,23 +3015,23 @@
         <v/>
       </c>
       <c r="V65" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA65" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF65" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK65" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP65" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -2987,23 +3049,23 @@
         <v/>
       </c>
       <c r="V66" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AA66" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AF66" s="4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK66" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="AP66" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
